--- a/Template_Expenses.xlsx
+++ b/Template_Expenses.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://farmfoods365-my.sharepoint.com/personal/nedwards_farmfoods_co_uk/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://farmfoods365-my.sharepoint.com/personal/nedwards_farmfoods_co_uk/Documents/Desktop/Expenses AI App/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="507" documentId="8_{13003DB7-9802-4EB4-85E1-72E9E493E541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F310623A-02E3-4173-BF55-2D591C62F6D4}"/>
+  <xr:revisionPtr revIDLastSave="510" documentId="8_{13003DB7-9802-4EB4-85E1-72E9E493E541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B6121A7-4EB2-42BA-9085-942D10892A53}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="223" xr2:uid="{3183D673-440C-4CE3-BB71-CA2E8D22CBB0}"/>
   </bookViews>
@@ -443,7 +443,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="38">
+  <borders count="44">
     <border>
       <left/>
       <right/>
@@ -928,6 +928,64 @@
       <bottom style="medium">
         <color indexed="8"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="8"/>
+      </left>
+      <right style="hair">
+        <color indexed="8"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="8"/>
+      </left>
+      <right style="hair">
+        <color indexed="8"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="8"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -975,7 +1033,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1042,6 +1100,36 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1483,7 +1571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB4BE928-8D03-4DC7-A125-236847F134C6}">
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
@@ -1550,343 +1638,1099 @@
       </c>
       <c r="J5" s="35"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="12"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="12"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
-      <c r="B8" s="31"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="12"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="6"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="12"/>
-    </row>
-    <row r="10" spans="1:10" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="6"/>
-      <c r="B10" s="31"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="20"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="20"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="20"/>
-    </row>
-    <row r="13" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="20"/>
-    </row>
-    <row r="14" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="20"/>
-    </row>
-    <row r="15" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="20"/>
-    </row>
-    <row r="16" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="20"/>
-    </row>
-    <row r="17" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="20"/>
-    </row>
-    <row r="18" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="20"/>
-    </row>
-    <row r="19" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="20"/>
-    </row>
-    <row r="20" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="20"/>
-    </row>
-    <row r="21" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="20"/>
-    </row>
-    <row r="22" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="20"/>
-    </row>
-    <row r="23" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="20"/>
-    </row>
-    <row r="24" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="20"/>
-    </row>
-    <row r="25" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="20"/>
-    </row>
-    <row r="26" spans="1:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="20"/>
-    </row>
-    <row r="27" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="21"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23" t="s">
+    <row r="6" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="37"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
+    </row>
+    <row r="7" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="37"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="46"/>
+    </row>
+    <row r="8" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="37"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="46"/>
+    </row>
+    <row r="9" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="37"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="46"/>
+    </row>
+    <row r="10" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="37"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="45"/>
+      <c r="J10" s="46"/>
+    </row>
+    <row r="11" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="37"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="46"/>
+    </row>
+    <row r="12" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="37"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="46"/>
+    </row>
+    <row r="13" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="37"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="45"/>
+      <c r="J13" s="46"/>
+    </row>
+    <row r="14" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="37"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="46"/>
+    </row>
+    <row r="15" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="37"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="46"/>
+    </row>
+    <row r="16" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="37"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="46"/>
+    </row>
+    <row r="17" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="37"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="46"/>
+    </row>
+    <row r="18" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="37"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="46"/>
+    </row>
+    <row r="19" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="37"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="46"/>
+    </row>
+    <row r="20" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="37"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="46"/>
+    </row>
+    <row r="21" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="37"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="46"/>
+    </row>
+    <row r="22" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="37"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="46"/>
+    </row>
+    <row r="23" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="37"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="46"/>
+    </row>
+    <row r="24" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="37"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="46"/>
+    </row>
+    <row r="25" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="37"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="46"/>
+    </row>
+    <row r="26" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="37"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="46"/>
+    </row>
+    <row r="27" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="37"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="46"/>
+    </row>
+    <row r="28" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="37"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="46"/>
+    </row>
+    <row r="29" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="37"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="46"/>
+    </row>
+    <row r="30" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="37"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="46"/>
+    </row>
+    <row r="31" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="37"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="42"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="44"/>
+      <c r="I31" s="45"/>
+      <c r="J31" s="46"/>
+    </row>
+    <row r="32" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="37"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="45"/>
+      <c r="J32" s="46"/>
+    </row>
+    <row r="33" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="37"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="44"/>
+      <c r="I33" s="45"/>
+      <c r="J33" s="46"/>
+    </row>
+    <row r="34" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="37"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="45"/>
+      <c r="J34" s="46"/>
+    </row>
+    <row r="35" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="37"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="44"/>
+      <c r="I35" s="45"/>
+      <c r="J35" s="46"/>
+    </row>
+    <row r="36" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="37"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="43"/>
+      <c r="H36" s="44"/>
+      <c r="I36" s="45"/>
+      <c r="J36" s="46"/>
+    </row>
+    <row r="37" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="37"/>
+      <c r="B37" s="38"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="40"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="42"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="44"/>
+      <c r="I37" s="45"/>
+      <c r="J37" s="46"/>
+    </row>
+    <row r="38" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="37"/>
+      <c r="B38" s="38"/>
+      <c r="C38" s="39"/>
+      <c r="D38" s="40"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="42"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="44"/>
+      <c r="I38" s="45"/>
+      <c r="J38" s="46"/>
+    </row>
+    <row r="39" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="37"/>
+      <c r="B39" s="38"/>
+      <c r="C39" s="39"/>
+      <c r="D39" s="40"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="44"/>
+      <c r="I39" s="45"/>
+      <c r="J39" s="46"/>
+    </row>
+    <row r="40" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="37"/>
+      <c r="B40" s="38"/>
+      <c r="C40" s="39"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="41"/>
+      <c r="F40" s="42"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="44"/>
+      <c r="I40" s="45"/>
+      <c r="J40" s="46"/>
+    </row>
+    <row r="41" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="37"/>
+      <c r="B41" s="38"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="40"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="42"/>
+      <c r="G41" s="43"/>
+      <c r="H41" s="44"/>
+      <c r="I41" s="45"/>
+      <c r="J41" s="46"/>
+    </row>
+    <row r="42" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="37"/>
+      <c r="B42" s="38"/>
+      <c r="C42" s="39"/>
+      <c r="D42" s="40"/>
+      <c r="E42" s="41"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="43"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="46"/>
+    </row>
+    <row r="43" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="37"/>
+      <c r="B43" s="38"/>
+      <c r="C43" s="39"/>
+      <c r="D43" s="40"/>
+      <c r="E43" s="41"/>
+      <c r="F43" s="42"/>
+      <c r="G43" s="43"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="45"/>
+      <c r="J43" s="46"/>
+    </row>
+    <row r="44" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="37"/>
+      <c r="B44" s="38"/>
+      <c r="C44" s="39"/>
+      <c r="D44" s="40"/>
+      <c r="E44" s="41"/>
+      <c r="F44" s="42"/>
+      <c r="G44" s="43"/>
+      <c r="H44" s="44"/>
+      <c r="I44" s="45"/>
+      <c r="J44" s="46"/>
+    </row>
+    <row r="45" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="37"/>
+      <c r="B45" s="38"/>
+      <c r="C45" s="39"/>
+      <c r="D45" s="40"/>
+      <c r="E45" s="41"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="43"/>
+      <c r="H45" s="44"/>
+      <c r="I45" s="45"/>
+      <c r="J45" s="46"/>
+    </row>
+    <row r="46" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="37"/>
+      <c r="B46" s="38"/>
+      <c r="C46" s="39"/>
+      <c r="D46" s="40"/>
+      <c r="E46" s="41"/>
+      <c r="F46" s="42"/>
+      <c r="G46" s="43"/>
+      <c r="H46" s="44"/>
+      <c r="I46" s="45"/>
+      <c r="J46" s="46"/>
+    </row>
+    <row r="47" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="37"/>
+      <c r="B47" s="38"/>
+      <c r="C47" s="39"/>
+      <c r="D47" s="40"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="42"/>
+      <c r="G47" s="43"/>
+      <c r="H47" s="44"/>
+      <c r="I47" s="45"/>
+      <c r="J47" s="46"/>
+    </row>
+    <row r="48" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="37"/>
+      <c r="B48" s="38"/>
+      <c r="C48" s="39"/>
+      <c r="D48" s="40"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="42"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="44"/>
+      <c r="I48" s="45"/>
+      <c r="J48" s="46"/>
+    </row>
+    <row r="49" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="37"/>
+      <c r="B49" s="38"/>
+      <c r="C49" s="39"/>
+      <c r="D49" s="40"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="42"/>
+      <c r="G49" s="43"/>
+      <c r="H49" s="44"/>
+      <c r="I49" s="45"/>
+      <c r="J49" s="46"/>
+    </row>
+    <row r="50" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="37"/>
+      <c r="B50" s="38"/>
+      <c r="C50" s="39"/>
+      <c r="D50" s="40"/>
+      <c r="E50" s="41"/>
+      <c r="F50" s="42"/>
+      <c r="G50" s="43"/>
+      <c r="H50" s="44"/>
+      <c r="I50" s="45"/>
+      <c r="J50" s="46"/>
+    </row>
+    <row r="51" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="37"/>
+      <c r="B51" s="38"/>
+      <c r="C51" s="39"/>
+      <c r="D51" s="40"/>
+      <c r="E51" s="41"/>
+      <c r="F51" s="42"/>
+      <c r="G51" s="43"/>
+      <c r="H51" s="44"/>
+      <c r="I51" s="45"/>
+      <c r="J51" s="46"/>
+    </row>
+    <row r="52" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="37"/>
+      <c r="B52" s="38"/>
+      <c r="C52" s="39"/>
+      <c r="D52" s="40"/>
+      <c r="E52" s="41"/>
+      <c r="F52" s="42"/>
+      <c r="G52" s="43"/>
+      <c r="H52" s="44"/>
+      <c r="I52" s="45"/>
+      <c r="J52" s="46"/>
+    </row>
+    <row r="53" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="37"/>
+      <c r="B53" s="38"/>
+      <c r="C53" s="39"/>
+      <c r="D53" s="40"/>
+      <c r="E53" s="41"/>
+      <c r="F53" s="42"/>
+      <c r="G53" s="43"/>
+      <c r="H53" s="44"/>
+      <c r="I53" s="45"/>
+      <c r="J53" s="46"/>
+    </row>
+    <row r="54" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="37"/>
+      <c r="B54" s="38"/>
+      <c r="C54" s="39"/>
+      <c r="D54" s="40"/>
+      <c r="E54" s="41"/>
+      <c r="F54" s="42"/>
+      <c r="G54" s="43"/>
+      <c r="H54" s="44"/>
+      <c r="I54" s="45"/>
+      <c r="J54" s="46"/>
+    </row>
+    <row r="55" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="37"/>
+      <c r="B55" s="38"/>
+      <c r="C55" s="39"/>
+      <c r="D55" s="40"/>
+      <c r="E55" s="41"/>
+      <c r="F55" s="42"/>
+      <c r="G55" s="43"/>
+      <c r="H55" s="44"/>
+      <c r="I55" s="45"/>
+      <c r="J55" s="46"/>
+    </row>
+    <row r="56" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="37"/>
+      <c r="B56" s="38"/>
+      <c r="C56" s="39"/>
+      <c r="D56" s="40"/>
+      <c r="E56" s="41"/>
+      <c r="F56" s="42"/>
+      <c r="G56" s="43"/>
+      <c r="H56" s="44"/>
+      <c r="I56" s="45"/>
+      <c r="J56" s="46"/>
+    </row>
+    <row r="57" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="37"/>
+      <c r="B57" s="38"/>
+      <c r="C57" s="39"/>
+      <c r="D57" s="40"/>
+      <c r="E57" s="41"/>
+      <c r="F57" s="42"/>
+      <c r="G57" s="43"/>
+      <c r="H57" s="44"/>
+      <c r="I57" s="45"/>
+      <c r="J57" s="46"/>
+    </row>
+    <row r="58" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="37"/>
+      <c r="B58" s="38"/>
+      <c r="C58" s="39"/>
+      <c r="D58" s="40"/>
+      <c r="E58" s="41"/>
+      <c r="F58" s="42"/>
+      <c r="G58" s="43"/>
+      <c r="H58" s="44"/>
+      <c r="I58" s="45"/>
+      <c r="J58" s="46"/>
+    </row>
+    <row r="59" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="37"/>
+      <c r="B59" s="38"/>
+      <c r="C59" s="39"/>
+      <c r="D59" s="40"/>
+      <c r="E59" s="41"/>
+      <c r="F59" s="42"/>
+      <c r="G59" s="43"/>
+      <c r="H59" s="44"/>
+      <c r="I59" s="45"/>
+      <c r="J59" s="46"/>
+    </row>
+    <row r="60" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="37"/>
+      <c r="B60" s="38"/>
+      <c r="C60" s="39"/>
+      <c r="D60" s="40"/>
+      <c r="E60" s="41"/>
+      <c r="F60" s="42"/>
+      <c r="G60" s="43"/>
+      <c r="H60" s="44"/>
+      <c r="I60" s="45"/>
+      <c r="J60" s="46"/>
+    </row>
+    <row r="61" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="37"/>
+      <c r="B61" s="38"/>
+      <c r="C61" s="39"/>
+      <c r="D61" s="40"/>
+      <c r="E61" s="41"/>
+      <c r="F61" s="42"/>
+      <c r="G61" s="43"/>
+      <c r="H61" s="44"/>
+      <c r="I61" s="45"/>
+      <c r="J61" s="46"/>
+    </row>
+    <row r="62" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="37"/>
+      <c r="B62" s="38"/>
+      <c r="C62" s="39"/>
+      <c r="D62" s="40"/>
+      <c r="E62" s="41"/>
+      <c r="F62" s="42"/>
+      <c r="G62" s="43"/>
+      <c r="H62" s="44"/>
+      <c r="I62" s="45"/>
+      <c r="J62" s="46"/>
+    </row>
+    <row r="63" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="37"/>
+      <c r="B63" s="38"/>
+      <c r="C63" s="39"/>
+      <c r="D63" s="40"/>
+      <c r="E63" s="41"/>
+      <c r="F63" s="42"/>
+      <c r="G63" s="43"/>
+      <c r="H63" s="44"/>
+      <c r="I63" s="45"/>
+      <c r="J63" s="46"/>
+    </row>
+    <row r="64" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="37"/>
+      <c r="B64" s="38"/>
+      <c r="C64" s="39"/>
+      <c r="D64" s="40"/>
+      <c r="E64" s="41"/>
+      <c r="F64" s="42"/>
+      <c r="G64" s="43"/>
+      <c r="H64" s="44"/>
+      <c r="I64" s="45"/>
+      <c r="J64" s="46"/>
+    </row>
+    <row r="65" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="37"/>
+      <c r="B65" s="38"/>
+      <c r="C65" s="39"/>
+      <c r="D65" s="40"/>
+      <c r="E65" s="41"/>
+      <c r="F65" s="42"/>
+      <c r="G65" s="43"/>
+      <c r="H65" s="44"/>
+      <c r="I65" s="45"/>
+      <c r="J65" s="46"/>
+    </row>
+    <row r="66" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="37"/>
+      <c r="B66" s="38"/>
+      <c r="C66" s="39"/>
+      <c r="D66" s="40"/>
+      <c r="E66" s="41"/>
+      <c r="F66" s="42"/>
+      <c r="G66" s="43"/>
+      <c r="H66" s="44"/>
+      <c r="I66" s="45"/>
+      <c r="J66" s="46"/>
+    </row>
+    <row r="67" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="37"/>
+      <c r="B67" s="38"/>
+      <c r="C67" s="39"/>
+      <c r="D67" s="40"/>
+      <c r="E67" s="41"/>
+      <c r="F67" s="42"/>
+      <c r="G67" s="43"/>
+      <c r="H67" s="44"/>
+      <c r="I67" s="45"/>
+      <c r="J67" s="46"/>
+    </row>
+    <row r="68" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="37"/>
+      <c r="B68" s="38"/>
+      <c r="C68" s="39"/>
+      <c r="D68" s="40"/>
+      <c r="E68" s="41"/>
+      <c r="F68" s="42"/>
+      <c r="G68" s="43"/>
+      <c r="H68" s="44"/>
+      <c r="I68" s="45"/>
+      <c r="J68" s="46"/>
+    </row>
+    <row r="69" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="6"/>
+      <c r="B69" s="31"/>
+      <c r="C69" s="7"/>
+      <c r="D69" s="8"/>
+      <c r="E69" s="9"/>
+      <c r="F69" s="10"/>
+      <c r="G69" s="9"/>
+      <c r="H69" s="10"/>
+      <c r="I69" s="11"/>
+      <c r="J69" s="12"/>
+    </row>
+    <row r="70" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="6"/>
+      <c r="B70" s="31"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="9"/>
+      <c r="F70" s="10"/>
+      <c r="G70" s="9"/>
+      <c r="H70" s="10"/>
+      <c r="I70" s="11"/>
+      <c r="J70" s="12"/>
+    </row>
+    <row r="71" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="6"/>
+      <c r="B71" s="31"/>
+      <c r="C71" s="7"/>
+      <c r="D71" s="8"/>
+      <c r="E71" s="9"/>
+      <c r="F71" s="10"/>
+      <c r="G71" s="9"/>
+      <c r="H71" s="10"/>
+      <c r="I71" s="11"/>
+      <c r="J71" s="12"/>
+    </row>
+    <row r="72" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="6"/>
+      <c r="B72" s="31"/>
+      <c r="C72" s="7"/>
+      <c r="D72" s="8"/>
+      <c r="E72" s="9"/>
+      <c r="F72" s="10"/>
+      <c r="G72" s="9"/>
+      <c r="H72" s="10"/>
+      <c r="I72" s="11"/>
+      <c r="J72" s="12"/>
+    </row>
+    <row r="73" spans="1:10" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="6"/>
+      <c r="B73" s="31"/>
+      <c r="C73" s="7"/>
+      <c r="D73" s="8"/>
+      <c r="E73" s="17"/>
+      <c r="F73" s="18"/>
+      <c r="G73" s="17"/>
+      <c r="H73" s="18"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="20"/>
+    </row>
+    <row r="74" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="13"/>
+      <c r="B74" s="14"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="17"/>
+      <c r="F74" s="18"/>
+      <c r="G74" s="17"/>
+      <c r="H74" s="18"/>
+      <c r="I74" s="19"/>
+      <c r="J74" s="20"/>
+    </row>
+    <row r="75" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="13"/>
+      <c r="B75" s="14"/>
+      <c r="C75" s="15"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="17"/>
+      <c r="F75" s="18"/>
+      <c r="G75" s="17"/>
+      <c r="H75" s="18"/>
+      <c r="I75" s="19"/>
+      <c r="J75" s="20"/>
+    </row>
+    <row r="76" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="13"/>
+      <c r="B76" s="14"/>
+      <c r="C76" s="7"/>
+      <c r="D76" s="16"/>
+      <c r="E76" s="17"/>
+      <c r="F76" s="18"/>
+      <c r="G76" s="17"/>
+      <c r="H76" s="18"/>
+      <c r="I76" s="19"/>
+      <c r="J76" s="20"/>
+    </row>
+    <row r="77" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="13"/>
+      <c r="B77" s="14"/>
+      <c r="C77" s="7"/>
+      <c r="D77" s="16"/>
+      <c r="E77" s="17"/>
+      <c r="F77" s="18"/>
+      <c r="G77" s="17"/>
+      <c r="H77" s="18"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="20"/>
+    </row>
+    <row r="78" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="13"/>
+      <c r="B78" s="14"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="16"/>
+      <c r="E78" s="17"/>
+      <c r="F78" s="18"/>
+      <c r="G78" s="17"/>
+      <c r="H78" s="18"/>
+      <c r="I78" s="19"/>
+      <c r="J78" s="20"/>
+    </row>
+    <row r="79" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="13"/>
+      <c r="B79" s="14"/>
+      <c r="C79" s="7"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="17"/>
+      <c r="F79" s="18"/>
+      <c r="G79" s="17"/>
+      <c r="H79" s="18"/>
+      <c r="I79" s="19"/>
+      <c r="J79" s="20"/>
+    </row>
+    <row r="80" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="13"/>
+      <c r="B80" s="14"/>
+      <c r="C80" s="7"/>
+      <c r="D80" s="16"/>
+      <c r="E80" s="17"/>
+      <c r="F80" s="18"/>
+      <c r="G80" s="17"/>
+      <c r="H80" s="18"/>
+      <c r="I80" s="19"/>
+      <c r="J80" s="20"/>
+    </row>
+    <row r="81" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="13"/>
+      <c r="B81" s="14"/>
+      <c r="C81" s="7"/>
+      <c r="D81" s="16"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="18"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="18"/>
+      <c r="I81" s="19"/>
+      <c r="J81" s="20"/>
+    </row>
+    <row r="82" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="13"/>
+      <c r="B82" s="14"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="16"/>
+      <c r="E82" s="17"/>
+      <c r="F82" s="18"/>
+      <c r="G82" s="17"/>
+      <c r="H82" s="18"/>
+      <c r="I82" s="19"/>
+      <c r="J82" s="20"/>
+    </row>
+    <row r="83" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="13"/>
+      <c r="B83" s="14"/>
+      <c r="C83" s="7"/>
+      <c r="D83" s="16"/>
+      <c r="E83" s="17"/>
+      <c r="F83" s="18"/>
+      <c r="G83" s="17"/>
+      <c r="H83" s="18"/>
+      <c r="I83" s="19"/>
+      <c r="J83" s="20"/>
+    </row>
+    <row r="84" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="13"/>
+      <c r="B84" s="14"/>
+      <c r="C84" s="7"/>
+      <c r="D84" s="16"/>
+      <c r="E84" s="17"/>
+      <c r="F84" s="18"/>
+      <c r="G84" s="17"/>
+      <c r="H84" s="18"/>
+      <c r="I84" s="19"/>
+      <c r="J84" s="20"/>
+    </row>
+    <row r="85" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="13"/>
+      <c r="B85" s="14"/>
+      <c r="C85" s="7"/>
+      <c r="D85" s="16"/>
+      <c r="E85" s="17"/>
+      <c r="F85" s="18"/>
+      <c r="G85" s="17"/>
+      <c r="H85" s="18"/>
+      <c r="I85" s="19"/>
+      <c r="J85" s="20"/>
+    </row>
+    <row r="86" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="13"/>
+      <c r="B86" s="14"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="16"/>
+      <c r="E86" s="17"/>
+      <c r="F86" s="18"/>
+      <c r="G86" s="17"/>
+      <c r="H86" s="18"/>
+      <c r="I86" s="19"/>
+      <c r="J86" s="20"/>
+    </row>
+    <row r="87" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="13"/>
+      <c r="B87" s="14"/>
+      <c r="C87" s="15"/>
+      <c r="D87" s="16"/>
+      <c r="E87" s="17"/>
+      <c r="F87" s="18"/>
+      <c r="G87" s="17"/>
+      <c r="H87" s="18"/>
+      <c r="I87" s="19"/>
+      <c r="J87" s="20"/>
+    </row>
+    <row r="88" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="13"/>
+      <c r="B88" s="14"/>
+      <c r="C88" s="15"/>
+      <c r="D88" s="16"/>
+      <c r="E88" s="17"/>
+      <c r="F88" s="18"/>
+      <c r="G88" s="17"/>
+      <c r="H88" s="18"/>
+      <c r="I88" s="19"/>
+      <c r="J88" s="20"/>
+    </row>
+    <row r="89" spans="1:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="13"/>
+      <c r="B89" s="14"/>
+      <c r="C89" s="15"/>
+      <c r="D89" s="16"/>
+      <c r="E89" s="17"/>
+      <c r="F89" s="18"/>
+      <c r="G89" s="17"/>
+      <c r="H89" s="18"/>
+      <c r="I89" s="19"/>
+      <c r="J89" s="20"/>
+    </row>
+    <row r="90" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="21"/>
+      <c r="B90" s="22"/>
+      <c r="C90" s="23"/>
+      <c r="D90" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E27" s="24"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="27" t="s">
+      <c r="E90" s="24"/>
+      <c r="F90" s="25"/>
+      <c r="G90" s="24"/>
+      <c r="H90" s="25"/>
+      <c r="I90" s="26"/>
+      <c r="J90" s="26"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B30" s="27"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="27" t="s">
+      <c r="B93" s="27"/>
+      <c r="C93" s="28"/>
+      <c r="D93" s="28"/>
+      <c r="E93" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="27"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="29" t="s">
+      <c r="F93" s="27"/>
+      <c r="G93" s="27"/>
+      <c r="H93" s="27"/>
+      <c r="I93" s="27"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="B32" s="30" t="s">
+      <c r="B95" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-    </row>
-    <row r="33" spans="1:9" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="30"/>
-      <c r="B33" s="30" t="s">
+      <c r="C95" s="30"/>
+      <c r="D95" s="30"/>
+      <c r="E95" s="30"/>
+      <c r="F95" s="30"/>
+      <c r="G95" s="30"/>
+      <c r="H95" s="30"/>
+      <c r="I95" s="30"/>
+    </row>
+    <row r="96" spans="1:10" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A96" s="30"/>
+      <c r="B96" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="30"/>
-      <c r="B34" s="30" t="s">
+      <c r="C96" s="30"/>
+      <c r="D96" s="30"/>
+      <c r="E96" s="30"/>
+      <c r="F96" s="30"/>
+      <c r="G96" s="30"/>
+      <c r="H96" s="30"/>
+      <c r="I96" s="30"/>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="30"/>
+      <c r="B97" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="30"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="30"/>
-      <c r="B35" s="30" t="s">
+      <c r="C97" s="30"/>
+      <c r="D97" s="30"/>
+      <c r="E97" s="30"/>
+      <c r="F97" s="30"/>
+      <c r="G97" s="30"/>
+      <c r="H97" s="30"/>
+      <c r="I97" s="30"/>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" s="30"/>
+      <c r="B98" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B36" s="30" t="s">
+      <c r="C98" s="30"/>
+      <c r="D98" s="30"/>
+      <c r="E98" s="30"/>
+      <c r="F98" s="30"/>
+      <c r="G98" s="30"/>
+      <c r="H98" s="30"/>
+      <c r="I98" s="30"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B99" s="30" t="s">
         <v>17</v>
       </c>
     </row>

--- a/Template_Expenses.xlsx
+++ b/Template_Expenses.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://farmfoods365-my.sharepoint.com/personal/nedwards_farmfoods_co_uk/Documents/Desktop/Expenses AI App/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="510" documentId="8_{13003DB7-9802-4EB4-85E1-72E9E493E541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B6121A7-4EB2-42BA-9085-942D10892A53}"/>
+  <xr:revisionPtr revIDLastSave="513" documentId="8_{13003DB7-9802-4EB4-85E1-72E9E493E541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3DD6108-1D48-43AF-8849-F1C176AF6E06}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="223" xr2:uid="{3183D673-440C-4CE3-BB71-CA2E8D22CBB0}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="223" xr2:uid="{3183D673-440C-4CE3-BB71-CA2E8D22CBB0}"/>
   </bookViews>
   <sheets>
     <sheet name="A4" sheetId="1" r:id="rId1"/>
@@ -443,7 +443,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="44">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -713,10 +713,8 @@
       <diagonal/>
     </border>
     <border>
-      <left style="hair">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
+      <left/>
+      <right style="hair">
         <color indexed="8"/>
       </right>
       <top/>
@@ -726,133 +724,79 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="8"/>
+      </left>
+      <right style="hair">
+        <color indexed="8"/>
+      </right>
+      <top style="hair">
+        <color indexed="8"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="8"/>
+      </left>
+      <right style="hair">
+        <color indexed="8"/>
+      </right>
+      <top style="hair">
+        <color indexed="8"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color indexed="8"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color indexed="8"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="hair">
+        <color indexed="8"/>
+      </right>
+      <top style="hair">
+        <color indexed="8"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="hair">
-        <color indexed="8"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="8"/>
-      </left>
-      <right style="medium">
-        <color indexed="8"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="8"/>
-      </left>
-      <right style="hair">
-        <color indexed="8"/>
-      </right>
-      <top style="hair">
-        <color indexed="8"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="8"/>
-      </left>
-      <right style="hair">
-        <color indexed="8"/>
-      </right>
-      <top style="hair">
-        <color indexed="8"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="8"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color indexed="8"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color indexed="8"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right style="hair">
-        <color indexed="8"/>
-      </right>
-      <top style="hair">
-        <color indexed="8"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top style="hair">
-        <color indexed="8"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color indexed="8"/>
-      </right>
-      <top style="hair">
-        <color indexed="8"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="8"/>
-      </left>
-      <right style="medium">
         <color indexed="8"/>
       </right>
       <top style="hair">
@@ -903,21 +847,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="hair">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top style="medium">
-        <color indexed="8"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="hair">
         <color indexed="8"/>
@@ -966,24 +895,6 @@
         <color indexed="8"/>
       </left>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="8"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -1033,7 +944,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1053,32 +964,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1086,9 +990,6 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1101,35 +1002,29 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1571,48 +1466,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB4BE928-8D03-4DC7-A125-236847F134C6}">
-  <dimension ref="A1:J99"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
     <col min="2" max="3" width="46" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="8.109375" customWidth="1"/>
-    <col min="6" max="6" width="3.6640625" customWidth="1"/>
-    <col min="7" max="7" width="8.109375" customWidth="1"/>
-    <col min="8" max="8" width="3.6640625" customWidth="1"/>
-    <col min="9" max="9" width="8.109375" customWidth="1"/>
-    <col min="10" max="10" width="3.6640625" customWidth="1"/>
+    <col min="5" max="7" width="8.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="1"/>
-      <c r="G3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-    </row>
-    <row r="4" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G3" s="30"/>
+    </row>
+    <row r="4" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
@@ -1625,1122 +1510,850 @@
       <c r="D5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="33"/>
-      <c r="G5" s="34" t="s">
+      <c r="F5" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="34"/>
-      <c r="I5" s="35" t="s">
+      <c r="G5" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="35"/>
-    </row>
-    <row r="6" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="37"/>
-      <c r="B6" s="38"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
-    </row>
-    <row r="7" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="37"/>
-      <c r="B7" s="38"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="46"/>
-    </row>
-    <row r="8" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="37"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="46"/>
-    </row>
-    <row r="9" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="37"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="46"/>
-    </row>
-    <row r="10" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="37"/>
-      <c r="B10" s="38"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="46"/>
-    </row>
-    <row r="11" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="37"/>
-      <c r="B11" s="38"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="46"/>
-    </row>
-    <row r="12" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="37"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="46"/>
-    </row>
-    <row r="13" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="37"/>
-      <c r="B13" s="38"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="46"/>
-    </row>
-    <row r="14" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="37"/>
-      <c r="B14" s="38"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="46"/>
-    </row>
-    <row r="15" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="37"/>
-      <c r="B15" s="38"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="44"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="46"/>
-    </row>
-    <row r="16" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="37"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="46"/>
-    </row>
-    <row r="17" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="37"/>
-      <c r="B17" s="38"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="46"/>
-    </row>
-    <row r="18" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="37"/>
-      <c r="B18" s="38"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="46"/>
-    </row>
-    <row r="19" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="37"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="43"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="46"/>
-    </row>
-    <row r="20" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="37"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="46"/>
-    </row>
-    <row r="21" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="37"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="46"/>
-    </row>
-    <row r="22" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="37"/>
-      <c r="B22" s="38"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="46"/>
-    </row>
-    <row r="23" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="37"/>
-      <c r="B23" s="38"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="43"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="46"/>
-    </row>
-    <row r="24" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="37"/>
-      <c r="B24" s="38"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="46"/>
-    </row>
-    <row r="25" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="37"/>
-      <c r="B25" s="38"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="46"/>
-    </row>
-    <row r="26" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="37"/>
-      <c r="B26" s="38"/>
-      <c r="C26" s="39"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="43"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="46"/>
-    </row>
-    <row r="27" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="37"/>
-      <c r="B27" s="38"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="43"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="46"/>
-    </row>
-    <row r="28" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="37"/>
-      <c r="B28" s="38"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="43"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="46"/>
-    </row>
-    <row r="29" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="37"/>
-      <c r="B29" s="38"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="43"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="46"/>
-    </row>
-    <row r="30" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="37"/>
-      <c r="B30" s="38"/>
-      <c r="C30" s="39"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="43"/>
-      <c r="H30" s="44"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="46"/>
-    </row>
-    <row r="31" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="37"/>
-      <c r="B31" s="38"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="42"/>
-      <c r="G31" s="43"/>
-      <c r="H31" s="44"/>
-      <c r="I31" s="45"/>
-      <c r="J31" s="46"/>
-    </row>
-    <row r="32" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="37"/>
-      <c r="B32" s="38"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="40"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="43"/>
-      <c r="H32" s="44"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="46"/>
-    </row>
-    <row r="33" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="37"/>
-      <c r="B33" s="38"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="43"/>
-      <c r="H33" s="44"/>
-      <c r="I33" s="45"/>
-      <c r="J33" s="46"/>
-    </row>
-    <row r="34" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="37"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="43"/>
-      <c r="H34" s="44"/>
-      <c r="I34" s="45"/>
-      <c r="J34" s="46"/>
-    </row>
-    <row r="35" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="37"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="39"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="41"/>
-      <c r="F35" s="42"/>
-      <c r="G35" s="43"/>
-      <c r="H35" s="44"/>
-      <c r="I35" s="45"/>
-      <c r="J35" s="46"/>
-    </row>
-    <row r="36" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="37"/>
-      <c r="B36" s="38"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="44"/>
-      <c r="I36" s="45"/>
-      <c r="J36" s="46"/>
-    </row>
-    <row r="37" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="37"/>
-      <c r="B37" s="38"/>
-      <c r="C37" s="39"/>
-      <c r="D37" s="40"/>
-      <c r="E37" s="41"/>
-      <c r="F37" s="42"/>
-      <c r="G37" s="43"/>
-      <c r="H37" s="44"/>
-      <c r="I37" s="45"/>
-      <c r="J37" s="46"/>
-    </row>
-    <row r="38" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="37"/>
-      <c r="B38" s="38"/>
-      <c r="C38" s="39"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="42"/>
-      <c r="G38" s="43"/>
-      <c r="H38" s="44"/>
-      <c r="I38" s="45"/>
-      <c r="J38" s="46"/>
-    </row>
-    <row r="39" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="37"/>
-      <c r="B39" s="38"/>
-      <c r="C39" s="39"/>
-      <c r="D39" s="40"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="42"/>
-      <c r="G39" s="43"/>
-      <c r="H39" s="44"/>
-      <c r="I39" s="45"/>
-      <c r="J39" s="46"/>
-    </row>
-    <row r="40" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="37"/>
-      <c r="B40" s="38"/>
-      <c r="C40" s="39"/>
-      <c r="D40" s="40"/>
-      <c r="E40" s="41"/>
-      <c r="F40" s="42"/>
-      <c r="G40" s="43"/>
-      <c r="H40" s="44"/>
-      <c r="I40" s="45"/>
-      <c r="J40" s="46"/>
-    </row>
-    <row r="41" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="37"/>
-      <c r="B41" s="38"/>
-      <c r="C41" s="39"/>
-      <c r="D41" s="40"/>
-      <c r="E41" s="41"/>
-      <c r="F41" s="42"/>
-      <c r="G41" s="43"/>
-      <c r="H41" s="44"/>
-      <c r="I41" s="45"/>
-      <c r="J41" s="46"/>
-    </row>
-    <row r="42" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="37"/>
-      <c r="B42" s="38"/>
-      <c r="C42" s="39"/>
-      <c r="D42" s="40"/>
-      <c r="E42" s="41"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="44"/>
-      <c r="I42" s="45"/>
-      <c r="J42" s="46"/>
-    </row>
-    <row r="43" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="37"/>
-      <c r="B43" s="38"/>
-      <c r="C43" s="39"/>
-      <c r="D43" s="40"/>
-      <c r="E43" s="41"/>
-      <c r="F43" s="42"/>
-      <c r="G43" s="43"/>
-      <c r="H43" s="44"/>
-      <c r="I43" s="45"/>
-      <c r="J43" s="46"/>
-    </row>
-    <row r="44" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="37"/>
-      <c r="B44" s="38"/>
-      <c r="C44" s="39"/>
-      <c r="D44" s="40"/>
-      <c r="E44" s="41"/>
-      <c r="F44" s="42"/>
-      <c r="G44" s="43"/>
-      <c r="H44" s="44"/>
-      <c r="I44" s="45"/>
-      <c r="J44" s="46"/>
-    </row>
-    <row r="45" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="37"/>
-      <c r="B45" s="38"/>
-      <c r="C45" s="39"/>
-      <c r="D45" s="40"/>
-      <c r="E45" s="41"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="43"/>
-      <c r="H45" s="44"/>
-      <c r="I45" s="45"/>
-      <c r="J45" s="46"/>
-    </row>
-    <row r="46" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="37"/>
-      <c r="B46" s="38"/>
-      <c r="C46" s="39"/>
-      <c r="D46" s="40"/>
-      <c r="E46" s="41"/>
-      <c r="F46" s="42"/>
-      <c r="G46" s="43"/>
-      <c r="H46" s="44"/>
-      <c r="I46" s="45"/>
-      <c r="J46" s="46"/>
-    </row>
-    <row r="47" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="37"/>
-      <c r="B47" s="38"/>
-      <c r="C47" s="39"/>
-      <c r="D47" s="40"/>
-      <c r="E47" s="41"/>
-      <c r="F47" s="42"/>
-      <c r="G47" s="43"/>
-      <c r="H47" s="44"/>
-      <c r="I47" s="45"/>
-      <c r="J47" s="46"/>
-    </row>
-    <row r="48" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="37"/>
-      <c r="B48" s="38"/>
-      <c r="C48" s="39"/>
-      <c r="D48" s="40"/>
-      <c r="E48" s="41"/>
-      <c r="F48" s="42"/>
-      <c r="G48" s="43"/>
-      <c r="H48" s="44"/>
-      <c r="I48" s="45"/>
-      <c r="J48" s="46"/>
-    </row>
-    <row r="49" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="37"/>
-      <c r="B49" s="38"/>
-      <c r="C49" s="39"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="42"/>
-      <c r="G49" s="43"/>
-      <c r="H49" s="44"/>
-      <c r="I49" s="45"/>
-      <c r="J49" s="46"/>
-    </row>
-    <row r="50" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="37"/>
-      <c r="B50" s="38"/>
-      <c r="C50" s="39"/>
-      <c r="D50" s="40"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="42"/>
-      <c r="G50" s="43"/>
-      <c r="H50" s="44"/>
-      <c r="I50" s="45"/>
-      <c r="J50" s="46"/>
-    </row>
-    <row r="51" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="37"/>
-      <c r="B51" s="38"/>
-      <c r="C51" s="39"/>
-      <c r="D51" s="40"/>
-      <c r="E51" s="41"/>
-      <c r="F51" s="42"/>
-      <c r="G51" s="43"/>
-      <c r="H51" s="44"/>
-      <c r="I51" s="45"/>
-      <c r="J51" s="46"/>
-    </row>
-    <row r="52" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="37"/>
-      <c r="B52" s="38"/>
-      <c r="C52" s="39"/>
-      <c r="D52" s="40"/>
-      <c r="E52" s="41"/>
-      <c r="F52" s="42"/>
-      <c r="G52" s="43"/>
-      <c r="H52" s="44"/>
-      <c r="I52" s="45"/>
-      <c r="J52" s="46"/>
-    </row>
-    <row r="53" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="37"/>
-      <c r="B53" s="38"/>
-      <c r="C53" s="39"/>
-      <c r="D53" s="40"/>
-      <c r="E53" s="41"/>
-      <c r="F53" s="42"/>
-      <c r="G53" s="43"/>
-      <c r="H53" s="44"/>
-      <c r="I53" s="45"/>
-      <c r="J53" s="46"/>
-    </row>
-    <row r="54" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="37"/>
-      <c r="B54" s="38"/>
-      <c r="C54" s="39"/>
-      <c r="D54" s="40"/>
-      <c r="E54" s="41"/>
-      <c r="F54" s="42"/>
-      <c r="G54" s="43"/>
-      <c r="H54" s="44"/>
-      <c r="I54" s="45"/>
-      <c r="J54" s="46"/>
-    </row>
-    <row r="55" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="37"/>
-      <c r="B55" s="38"/>
-      <c r="C55" s="39"/>
-      <c r="D55" s="40"/>
-      <c r="E55" s="41"/>
-      <c r="F55" s="42"/>
-      <c r="G55" s="43"/>
-      <c r="H55" s="44"/>
-      <c r="I55" s="45"/>
-      <c r="J55" s="46"/>
-    </row>
-    <row r="56" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="37"/>
-      <c r="B56" s="38"/>
-      <c r="C56" s="39"/>
-      <c r="D56" s="40"/>
-      <c r="E56" s="41"/>
-      <c r="F56" s="42"/>
-      <c r="G56" s="43"/>
-      <c r="H56" s="44"/>
-      <c r="I56" s="45"/>
-      <c r="J56" s="46"/>
-    </row>
-    <row r="57" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="37"/>
-      <c r="B57" s="38"/>
-      <c r="C57" s="39"/>
-      <c r="D57" s="40"/>
-      <c r="E57" s="41"/>
-      <c r="F57" s="42"/>
-      <c r="G57" s="43"/>
-      <c r="H57" s="44"/>
-      <c r="I57" s="45"/>
-      <c r="J57" s="46"/>
-    </row>
-    <row r="58" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="37"/>
-      <c r="B58" s="38"/>
-      <c r="C58" s="39"/>
-      <c r="D58" s="40"/>
-      <c r="E58" s="41"/>
-      <c r="F58" s="42"/>
-      <c r="G58" s="43"/>
-      <c r="H58" s="44"/>
-      <c r="I58" s="45"/>
-      <c r="J58" s="46"/>
-    </row>
-    <row r="59" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="37"/>
-      <c r="B59" s="38"/>
-      <c r="C59" s="39"/>
-      <c r="D59" s="40"/>
-      <c r="E59" s="41"/>
-      <c r="F59" s="42"/>
-      <c r="G59" s="43"/>
-      <c r="H59" s="44"/>
-      <c r="I59" s="45"/>
-      <c r="J59" s="46"/>
-    </row>
-    <row r="60" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="37"/>
-      <c r="B60" s="38"/>
-      <c r="C60" s="39"/>
-      <c r="D60" s="40"/>
-      <c r="E60" s="41"/>
-      <c r="F60" s="42"/>
-      <c r="G60" s="43"/>
-      <c r="H60" s="44"/>
-      <c r="I60" s="45"/>
-      <c r="J60" s="46"/>
-    </row>
-    <row r="61" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="37"/>
-      <c r="B61" s="38"/>
-      <c r="C61" s="39"/>
-      <c r="D61" s="40"/>
-      <c r="E61" s="41"/>
-      <c r="F61" s="42"/>
-      <c r="G61" s="43"/>
-      <c r="H61" s="44"/>
-      <c r="I61" s="45"/>
-      <c r="J61" s="46"/>
-    </row>
-    <row r="62" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="37"/>
-      <c r="B62" s="38"/>
-      <c r="C62" s="39"/>
-      <c r="D62" s="40"/>
-      <c r="E62" s="41"/>
-      <c r="F62" s="42"/>
-      <c r="G62" s="43"/>
-      <c r="H62" s="44"/>
-      <c r="I62" s="45"/>
-      <c r="J62" s="46"/>
-    </row>
-    <row r="63" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="37"/>
-      <c r="B63" s="38"/>
-      <c r="C63" s="39"/>
-      <c r="D63" s="40"/>
-      <c r="E63" s="41"/>
-      <c r="F63" s="42"/>
-      <c r="G63" s="43"/>
-      <c r="H63" s="44"/>
-      <c r="I63" s="45"/>
-      <c r="J63" s="46"/>
-    </row>
-    <row r="64" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="37"/>
-      <c r="B64" s="38"/>
-      <c r="C64" s="39"/>
-      <c r="D64" s="40"/>
-      <c r="E64" s="41"/>
-      <c r="F64" s="42"/>
-      <c r="G64" s="43"/>
-      <c r="H64" s="44"/>
-      <c r="I64" s="45"/>
-      <c r="J64" s="46"/>
-    </row>
-    <row r="65" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="37"/>
-      <c r="B65" s="38"/>
-      <c r="C65" s="39"/>
-      <c r="D65" s="40"/>
-      <c r="E65" s="41"/>
-      <c r="F65" s="42"/>
-      <c r="G65" s="43"/>
-      <c r="H65" s="44"/>
-      <c r="I65" s="45"/>
-      <c r="J65" s="46"/>
-    </row>
-    <row r="66" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="37"/>
-      <c r="B66" s="38"/>
-      <c r="C66" s="39"/>
-      <c r="D66" s="40"/>
-      <c r="E66" s="41"/>
-      <c r="F66" s="42"/>
-      <c r="G66" s="43"/>
-      <c r="H66" s="44"/>
-      <c r="I66" s="45"/>
-      <c r="J66" s="46"/>
-    </row>
-    <row r="67" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="37"/>
-      <c r="B67" s="38"/>
-      <c r="C67" s="39"/>
-      <c r="D67" s="40"/>
-      <c r="E67" s="41"/>
-      <c r="F67" s="42"/>
-      <c r="G67" s="43"/>
-      <c r="H67" s="44"/>
-      <c r="I67" s="45"/>
-      <c r="J67" s="46"/>
-    </row>
-    <row r="68" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="37"/>
-      <c r="B68" s="38"/>
-      <c r="C68" s="39"/>
-      <c r="D68" s="40"/>
-      <c r="E68" s="41"/>
-      <c r="F68" s="42"/>
-      <c r="G68" s="43"/>
-      <c r="H68" s="44"/>
-      <c r="I68" s="45"/>
-      <c r="J68" s="46"/>
-    </row>
-    <row r="69" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="31"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="37"/>
+    </row>
+    <row r="7" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="31"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="37"/>
+    </row>
+    <row r="8" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="31"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="37"/>
+    </row>
+    <row r="9" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="31"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="37"/>
+    </row>
+    <row r="10" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="31"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="37"/>
+    </row>
+    <row r="11" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="31"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="37"/>
+    </row>
+    <row r="12" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="31"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="37"/>
+    </row>
+    <row r="13" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="31"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="37"/>
+    </row>
+    <row r="14" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="31"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="37"/>
+    </row>
+    <row r="15" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="31"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="37"/>
+    </row>
+    <row r="16" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="31"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="37"/>
+    </row>
+    <row r="17" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="31"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="37"/>
+    </row>
+    <row r="18" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="31"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="37"/>
+    </row>
+    <row r="19" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="31"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="37"/>
+    </row>
+    <row r="20" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="31"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="37"/>
+    </row>
+    <row r="21" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="31"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="37"/>
+    </row>
+    <row r="22" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="31"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="37"/>
+    </row>
+    <row r="23" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="31"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="37"/>
+    </row>
+    <row r="24" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="31"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="37"/>
+    </row>
+    <row r="25" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="31"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="37"/>
+    </row>
+    <row r="26" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="31"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="37"/>
+    </row>
+    <row r="27" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="31"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="37"/>
+    </row>
+    <row r="28" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="31"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="37"/>
+    </row>
+    <row r="29" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="31"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="37"/>
+    </row>
+    <row r="30" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="31"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="37"/>
+    </row>
+    <row r="31" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="31"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="37"/>
+    </row>
+    <row r="32" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="31"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="37"/>
+    </row>
+    <row r="33" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="31"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="37"/>
+    </row>
+    <row r="34" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="31"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="37"/>
+    </row>
+    <row r="35" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="31"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="36"/>
+      <c r="G35" s="37"/>
+    </row>
+    <row r="36" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="31"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="37"/>
+    </row>
+    <row r="37" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="31"/>
+      <c r="B37" s="32"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="36"/>
+      <c r="G37" s="37"/>
+    </row>
+    <row r="38" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="31"/>
+      <c r="B38" s="32"/>
+      <c r="C38" s="33"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="37"/>
+    </row>
+    <row r="39" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="31"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="33"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="35"/>
+      <c r="F39" s="36"/>
+      <c r="G39" s="37"/>
+    </row>
+    <row r="40" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="31"/>
+      <c r="B40" s="32"/>
+      <c r="C40" s="33"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="37"/>
+    </row>
+    <row r="41" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="31"/>
+      <c r="B41" s="32"/>
+      <c r="C41" s="33"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="37"/>
+    </row>
+    <row r="42" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="31"/>
+      <c r="B42" s="32"/>
+      <c r="C42" s="33"/>
+      <c r="D42" s="34"/>
+      <c r="E42" s="35"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="37"/>
+    </row>
+    <row r="43" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="31"/>
+      <c r="B43" s="32"/>
+      <c r="C43" s="33"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="35"/>
+      <c r="F43" s="36"/>
+      <c r="G43" s="37"/>
+    </row>
+    <row r="44" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="31"/>
+      <c r="B44" s="32"/>
+      <c r="C44" s="33"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="35"/>
+      <c r="F44" s="36"/>
+      <c r="G44" s="37"/>
+    </row>
+    <row r="45" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="31"/>
+      <c r="B45" s="32"/>
+      <c r="C45" s="33"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="35"/>
+      <c r="F45" s="36"/>
+      <c r="G45" s="37"/>
+    </row>
+    <row r="46" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="31"/>
+      <c r="B46" s="32"/>
+      <c r="C46" s="33"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="35"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="37"/>
+    </row>
+    <row r="47" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="31"/>
+      <c r="B47" s="32"/>
+      <c r="C47" s="33"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="35"/>
+      <c r="F47" s="36"/>
+      <c r="G47" s="37"/>
+    </row>
+    <row r="48" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="31"/>
+      <c r="B48" s="32"/>
+      <c r="C48" s="33"/>
+      <c r="D48" s="34"/>
+      <c r="E48" s="35"/>
+      <c r="F48" s="36"/>
+      <c r="G48" s="37"/>
+    </row>
+    <row r="49" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="31"/>
+      <c r="B49" s="32"/>
+      <c r="C49" s="33"/>
+      <c r="D49" s="34"/>
+      <c r="E49" s="35"/>
+      <c r="F49" s="36"/>
+      <c r="G49" s="37"/>
+    </row>
+    <row r="50" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="31"/>
+      <c r="B50" s="32"/>
+      <c r="C50" s="33"/>
+      <c r="D50" s="34"/>
+      <c r="E50" s="35"/>
+      <c r="F50" s="36"/>
+      <c r="G50" s="37"/>
+    </row>
+    <row r="51" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="31"/>
+      <c r="B51" s="32"/>
+      <c r="C51" s="33"/>
+      <c r="D51" s="34"/>
+      <c r="E51" s="35"/>
+      <c r="F51" s="36"/>
+      <c r="G51" s="37"/>
+    </row>
+    <row r="52" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="31"/>
+      <c r="B52" s="32"/>
+      <c r="C52" s="33"/>
+      <c r="D52" s="34"/>
+      <c r="E52" s="35"/>
+      <c r="F52" s="36"/>
+      <c r="G52" s="37"/>
+    </row>
+    <row r="53" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="31"/>
+      <c r="B53" s="32"/>
+      <c r="C53" s="33"/>
+      <c r="D53" s="34"/>
+      <c r="E53" s="35"/>
+      <c r="F53" s="36"/>
+      <c r="G53" s="37"/>
+    </row>
+    <row r="54" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="31"/>
+      <c r="B54" s="32"/>
+      <c r="C54" s="33"/>
+      <c r="D54" s="34"/>
+      <c r="E54" s="35"/>
+      <c r="F54" s="36"/>
+      <c r="G54" s="37"/>
+    </row>
+    <row r="55" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="31"/>
+      <c r="B55" s="32"/>
+      <c r="C55" s="33"/>
+      <c r="D55" s="34"/>
+      <c r="E55" s="35"/>
+      <c r="F55" s="36"/>
+      <c r="G55" s="37"/>
+    </row>
+    <row r="56" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="31"/>
+      <c r="B56" s="32"/>
+      <c r="C56" s="33"/>
+      <c r="D56" s="34"/>
+      <c r="E56" s="35"/>
+      <c r="F56" s="36"/>
+      <c r="G56" s="37"/>
+    </row>
+    <row r="57" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="31"/>
+      <c r="B57" s="32"/>
+      <c r="C57" s="33"/>
+      <c r="D57" s="34"/>
+      <c r="E57" s="35"/>
+      <c r="F57" s="36"/>
+      <c r="G57" s="37"/>
+    </row>
+    <row r="58" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="31"/>
+      <c r="B58" s="32"/>
+      <c r="C58" s="33"/>
+      <c r="D58" s="34"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="36"/>
+      <c r="G58" s="37"/>
+    </row>
+    <row r="59" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="31"/>
+      <c r="B59" s="32"/>
+      <c r="C59" s="33"/>
+      <c r="D59" s="34"/>
+      <c r="E59" s="35"/>
+      <c r="F59" s="36"/>
+      <c r="G59" s="37"/>
+    </row>
+    <row r="60" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="31"/>
+      <c r="B60" s="32"/>
+      <c r="C60" s="33"/>
+      <c r="D60" s="34"/>
+      <c r="E60" s="35"/>
+      <c r="F60" s="36"/>
+      <c r="G60" s="37"/>
+    </row>
+    <row r="61" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="31"/>
+      <c r="B61" s="32"/>
+      <c r="C61" s="33"/>
+      <c r="D61" s="34"/>
+      <c r="E61" s="35"/>
+      <c r="F61" s="36"/>
+      <c r="G61" s="37"/>
+    </row>
+    <row r="62" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="31"/>
+      <c r="B62" s="32"/>
+      <c r="C62" s="33"/>
+      <c r="D62" s="34"/>
+      <c r="E62" s="35"/>
+      <c r="F62" s="36"/>
+      <c r="G62" s="37"/>
+    </row>
+    <row r="63" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="31"/>
+      <c r="B63" s="32"/>
+      <c r="C63" s="33"/>
+      <c r="D63" s="34"/>
+      <c r="E63" s="35"/>
+      <c r="F63" s="36"/>
+      <c r="G63" s="37"/>
+    </row>
+    <row r="64" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="31"/>
+      <c r="B64" s="32"/>
+      <c r="C64" s="33"/>
+      <c r="D64" s="34"/>
+      <c r="E64" s="35"/>
+      <c r="F64" s="36"/>
+      <c r="G64" s="37"/>
+    </row>
+    <row r="65" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="31"/>
+      <c r="B65" s="32"/>
+      <c r="C65" s="33"/>
+      <c r="D65" s="34"/>
+      <c r="E65" s="35"/>
+      <c r="F65" s="36"/>
+      <c r="G65" s="37"/>
+    </row>
+    <row r="66" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="31"/>
+      <c r="B66" s="32"/>
+      <c r="C66" s="33"/>
+      <c r="D66" s="34"/>
+      <c r="E66" s="35"/>
+      <c r="F66" s="36"/>
+      <c r="G66" s="37"/>
+    </row>
+    <row r="67" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="31"/>
+      <c r="B67" s="32"/>
+      <c r="C67" s="33"/>
+      <c r="D67" s="34"/>
+      <c r="E67" s="35"/>
+      <c r="F67" s="36"/>
+      <c r="G67" s="37"/>
+    </row>
+    <row r="68" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="31"/>
+      <c r="B68" s="32"/>
+      <c r="C68" s="33"/>
+      <c r="D68" s="34"/>
+      <c r="E68" s="35"/>
+      <c r="F68" s="36"/>
+      <c r="G68" s="37"/>
+    </row>
+    <row r="69" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6"/>
-      <c r="B69" s="31"/>
+      <c r="B69" s="26"/>
       <c r="C69" s="7"/>
       <c r="D69" s="8"/>
       <c r="E69" s="9"/>
-      <c r="F69" s="10"/>
-      <c r="G69" s="9"/>
-      <c r="H69" s="10"/>
-      <c r="I69" s="11"/>
-      <c r="J69" s="12"/>
-    </row>
-    <row r="70" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F69" s="9"/>
+      <c r="G69" s="10"/>
+    </row>
+    <row r="70" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6"/>
-      <c r="B70" s="31"/>
+      <c r="B70" s="26"/>
       <c r="C70" s="7"/>
       <c r="D70" s="8"/>
       <c r="E70" s="9"/>
-      <c r="F70" s="10"/>
-      <c r="G70" s="9"/>
-      <c r="H70" s="10"/>
-      <c r="I70" s="11"/>
-      <c r="J70" s="12"/>
-    </row>
-    <row r="71" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F70" s="9"/>
+      <c r="G70" s="10"/>
+    </row>
+    <row r="71" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6"/>
-      <c r="B71" s="31"/>
+      <c r="B71" s="26"/>
       <c r="C71" s="7"/>
       <c r="D71" s="8"/>
       <c r="E71" s="9"/>
-      <c r="F71" s="10"/>
-      <c r="G71" s="9"/>
-      <c r="H71" s="10"/>
-      <c r="I71" s="11"/>
-      <c r="J71" s="12"/>
-    </row>
-    <row r="72" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F71" s="9"/>
+      <c r="G71" s="10"/>
+    </row>
+    <row r="72" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6"/>
-      <c r="B72" s="31"/>
+      <c r="B72" s="26"/>
       <c r="C72" s="7"/>
       <c r="D72" s="8"/>
       <c r="E72" s="9"/>
-      <c r="F72" s="10"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="10"/>
-      <c r="I72" s="11"/>
-      <c r="J72" s="12"/>
-    </row>
-    <row r="73" spans="1:10" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F72" s="9"/>
+      <c r="G72" s="10"/>
+    </row>
+    <row r="73" spans="1:7" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="6"/>
-      <c r="B73" s="31"/>
+      <c r="B73" s="26"/>
       <c r="C73" s="7"/>
       <c r="D73" s="8"/>
-      <c r="E73" s="17"/>
-      <c r="F73" s="18"/>
-      <c r="G73" s="17"/>
-      <c r="H73" s="18"/>
-      <c r="I73" s="19"/>
-      <c r="J73" s="20"/>
-    </row>
-    <row r="74" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="13"/>
-      <c r="B74" s="14"/>
+      <c r="E73" s="15"/>
+      <c r="F73" s="15"/>
+      <c r="G73" s="16"/>
+    </row>
+    <row r="74" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="11"/>
+      <c r="B74" s="12"/>
       <c r="C74" s="7"/>
-      <c r="D74" s="16"/>
-      <c r="E74" s="17"/>
-      <c r="F74" s="18"/>
-      <c r="G74" s="17"/>
-      <c r="H74" s="18"/>
-      <c r="I74" s="19"/>
-      <c r="J74" s="20"/>
-    </row>
-    <row r="75" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="13"/>
-      <c r="B75" s="14"/>
-      <c r="C75" s="15"/>
-      <c r="D75" s="16"/>
-      <c r="E75" s="17"/>
-      <c r="F75" s="18"/>
-      <c r="G75" s="17"/>
-      <c r="H75" s="18"/>
-      <c r="I75" s="19"/>
-      <c r="J75" s="20"/>
-    </row>
-    <row r="76" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="13"/>
-      <c r="B76" s="14"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="15"/>
+      <c r="F74" s="15"/>
+      <c r="G74" s="16"/>
+    </row>
+    <row r="75" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="11"/>
+      <c r="B75" s="12"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="15"/>
+      <c r="F75" s="15"/>
+      <c r="G75" s="16"/>
+    </row>
+    <row r="76" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="11"/>
+      <c r="B76" s="12"/>
       <c r="C76" s="7"/>
-      <c r="D76" s="16"/>
-      <c r="E76" s="17"/>
-      <c r="F76" s="18"/>
-      <c r="G76" s="17"/>
-      <c r="H76" s="18"/>
-      <c r="I76" s="19"/>
-      <c r="J76" s="20"/>
-    </row>
-    <row r="77" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="13"/>
-      <c r="B77" s="14"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="15"/>
+      <c r="F76" s="15"/>
+      <c r="G76" s="16"/>
+    </row>
+    <row r="77" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="11"/>
+      <c r="B77" s="12"/>
       <c r="C77" s="7"/>
-      <c r="D77" s="16"/>
-      <c r="E77" s="17"/>
-      <c r="F77" s="18"/>
-      <c r="G77" s="17"/>
-      <c r="H77" s="18"/>
-      <c r="I77" s="19"/>
-      <c r="J77" s="20"/>
-    </row>
-    <row r="78" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="13"/>
-      <c r="B78" s="14"/>
+      <c r="D77" s="14"/>
+      <c r="E77" s="15"/>
+      <c r="F77" s="15"/>
+      <c r="G77" s="16"/>
+    </row>
+    <row r="78" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="11"/>
+      <c r="B78" s="12"/>
       <c r="C78" s="7"/>
-      <c r="D78" s="16"/>
-      <c r="E78" s="17"/>
-      <c r="F78" s="18"/>
-      <c r="G78" s="17"/>
-      <c r="H78" s="18"/>
-      <c r="I78" s="19"/>
-      <c r="J78" s="20"/>
-    </row>
-    <row r="79" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="13"/>
-      <c r="B79" s="14"/>
+      <c r="D78" s="14"/>
+      <c r="E78" s="15"/>
+      <c r="F78" s="15"/>
+      <c r="G78" s="16"/>
+    </row>
+    <row r="79" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="11"/>
+      <c r="B79" s="12"/>
       <c r="C79" s="7"/>
-      <c r="D79" s="16"/>
-      <c r="E79" s="17"/>
-      <c r="F79" s="18"/>
-      <c r="G79" s="17"/>
-      <c r="H79" s="18"/>
-      <c r="I79" s="19"/>
-      <c r="J79" s="20"/>
-    </row>
-    <row r="80" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="13"/>
-      <c r="B80" s="14"/>
+      <c r="D79" s="14"/>
+      <c r="E79" s="15"/>
+      <c r="F79" s="15"/>
+      <c r="G79" s="16"/>
+    </row>
+    <row r="80" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="11"/>
+      <c r="B80" s="12"/>
       <c r="C80" s="7"/>
-      <c r="D80" s="16"/>
-      <c r="E80" s="17"/>
-      <c r="F80" s="18"/>
-      <c r="G80" s="17"/>
-      <c r="H80" s="18"/>
-      <c r="I80" s="19"/>
-      <c r="J80" s="20"/>
-    </row>
-    <row r="81" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="13"/>
-      <c r="B81" s="14"/>
+      <c r="D80" s="14"/>
+      <c r="E80" s="15"/>
+      <c r="F80" s="15"/>
+      <c r="G80" s="16"/>
+    </row>
+    <row r="81" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="11"/>
+      <c r="B81" s="12"/>
       <c r="C81" s="7"/>
-      <c r="D81" s="16"/>
-      <c r="E81" s="17"/>
-      <c r="F81" s="18"/>
-      <c r="G81" s="17"/>
-      <c r="H81" s="18"/>
-      <c r="I81" s="19"/>
-      <c r="J81" s="20"/>
-    </row>
-    <row r="82" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="13"/>
-      <c r="B82" s="14"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="15"/>
+      <c r="F81" s="15"/>
+      <c r="G81" s="16"/>
+    </row>
+    <row r="82" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="11"/>
+      <c r="B82" s="12"/>
       <c r="C82" s="7"/>
-      <c r="D82" s="16"/>
-      <c r="E82" s="17"/>
-      <c r="F82" s="18"/>
-      <c r="G82" s="17"/>
-      <c r="H82" s="18"/>
-      <c r="I82" s="19"/>
-      <c r="J82" s="20"/>
-    </row>
-    <row r="83" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="13"/>
-      <c r="B83" s="14"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="15"/>
+      <c r="F82" s="15"/>
+      <c r="G82" s="16"/>
+    </row>
+    <row r="83" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="11"/>
+      <c r="B83" s="12"/>
       <c r="C83" s="7"/>
-      <c r="D83" s="16"/>
-      <c r="E83" s="17"/>
-      <c r="F83" s="18"/>
-      <c r="G83" s="17"/>
-      <c r="H83" s="18"/>
-      <c r="I83" s="19"/>
-      <c r="J83" s="20"/>
-    </row>
-    <row r="84" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="13"/>
-      <c r="B84" s="14"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="15"/>
+      <c r="F83" s="15"/>
+      <c r="G83" s="16"/>
+    </row>
+    <row r="84" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="11"/>
+      <c r="B84" s="12"/>
       <c r="C84" s="7"/>
-      <c r="D84" s="16"/>
-      <c r="E84" s="17"/>
-      <c r="F84" s="18"/>
-      <c r="G84" s="17"/>
-      <c r="H84" s="18"/>
-      <c r="I84" s="19"/>
-      <c r="J84" s="20"/>
-    </row>
-    <row r="85" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="13"/>
-      <c r="B85" s="14"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="15"/>
+      <c r="F84" s="15"/>
+      <c r="G84" s="16"/>
+    </row>
+    <row r="85" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="11"/>
+      <c r="B85" s="12"/>
       <c r="C85" s="7"/>
-      <c r="D85" s="16"/>
-      <c r="E85" s="17"/>
-      <c r="F85" s="18"/>
-      <c r="G85" s="17"/>
-      <c r="H85" s="18"/>
-      <c r="I85" s="19"/>
-      <c r="J85" s="20"/>
-    </row>
-    <row r="86" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="13"/>
-      <c r="B86" s="14"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="15"/>
+      <c r="F85" s="15"/>
+      <c r="G85" s="16"/>
+    </row>
+    <row r="86" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="11"/>
+      <c r="B86" s="12"/>
       <c r="C86" s="7"/>
-      <c r="D86" s="16"/>
-      <c r="E86" s="17"/>
-      <c r="F86" s="18"/>
-      <c r="G86" s="17"/>
-      <c r="H86" s="18"/>
-      <c r="I86" s="19"/>
-      <c r="J86" s="20"/>
-    </row>
-    <row r="87" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="13"/>
-      <c r="B87" s="14"/>
-      <c r="C87" s="15"/>
-      <c r="D87" s="16"/>
-      <c r="E87" s="17"/>
-      <c r="F87" s="18"/>
-      <c r="G87" s="17"/>
-      <c r="H87" s="18"/>
-      <c r="I87" s="19"/>
-      <c r="J87" s="20"/>
-    </row>
-    <row r="88" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="13"/>
-      <c r="B88" s="14"/>
-      <c r="C88" s="15"/>
-      <c r="D88" s="16"/>
-      <c r="E88" s="17"/>
-      <c r="F88" s="18"/>
-      <c r="G88" s="17"/>
-      <c r="H88" s="18"/>
-      <c r="I88" s="19"/>
-      <c r="J88" s="20"/>
-    </row>
-    <row r="89" spans="1:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="13"/>
-      <c r="B89" s="14"/>
-      <c r="C89" s="15"/>
-      <c r="D89" s="16"/>
-      <c r="E89" s="17"/>
-      <c r="F89" s="18"/>
-      <c r="G89" s="17"/>
-      <c r="H89" s="18"/>
-      <c r="I89" s="19"/>
-      <c r="J89" s="20"/>
-    </row>
-    <row r="90" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="21"/>
-      <c r="B90" s="22"/>
-      <c r="C90" s="23"/>
-      <c r="D90" s="23" t="s">
+      <c r="D86" s="14"/>
+      <c r="E86" s="15"/>
+      <c r="F86" s="15"/>
+      <c r="G86" s="16"/>
+    </row>
+    <row r="87" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="11"/>
+      <c r="B87" s="12"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="15"/>
+      <c r="F87" s="15"/>
+      <c r="G87" s="16"/>
+    </row>
+    <row r="88" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="15"/>
+      <c r="F88" s="15"/>
+      <c r="G88" s="16"/>
+    </row>
+    <row r="89" spans="1:7" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="11"/>
+      <c r="B89" s="12"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="15"/>
+      <c r="F89" s="15"/>
+      <c r="G89" s="16"/>
+    </row>
+    <row r="90" spans="1:7" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="17"/>
+      <c r="B90" s="18"/>
+      <c r="C90" s="19"/>
+      <c r="D90" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="E90" s="24"/>
-      <c r="F90" s="25"/>
-      <c r="G90" s="24"/>
-      <c r="H90" s="25"/>
-      <c r="I90" s="26"/>
-      <c r="J90" s="26"/>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A93" s="27" t="s">
+      <c r="E90" s="20"/>
+      <c r="F90" s="20"/>
+      <c r="G90" s="21"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B93" s="27"/>
-      <c r="C93" s="28"/>
-      <c r="D93" s="28"/>
-      <c r="E93" s="27" t="s">
+      <c r="B93" s="22"/>
+      <c r="C93" s="23"/>
+      <c r="D93" s="23"/>
+      <c r="E93" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="F93" s="27"/>
-      <c r="G93" s="27"/>
-      <c r="H93" s="27"/>
-      <c r="I93" s="27"/>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95" s="29" t="s">
+      <c r="F93" s="22"/>
+      <c r="G93" s="22"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="B95" s="30" t="s">
+      <c r="B95" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="C95" s="30"/>
-      <c r="D95" s="30"/>
-      <c r="E95" s="30"/>
-      <c r="F95" s="30"/>
-      <c r="G95" s="30"/>
-      <c r="H95" s="30"/>
-      <c r="I95" s="30"/>
-    </row>
-    <row r="96" spans="1:10" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A96" s="30"/>
-      <c r="B96" s="30" t="s">
+      <c r="C95" s="25"/>
+      <c r="D95" s="25"/>
+      <c r="E95" s="25"/>
+      <c r="F95" s="25"/>
+      <c r="G95" s="25"/>
+    </row>
+    <row r="96" spans="1:7" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A96" s="25"/>
+      <c r="B96" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="C96" s="30"/>
-      <c r="D96" s="30"/>
-      <c r="E96" s="30"/>
-      <c r="F96" s="30"/>
-      <c r="G96" s="30"/>
-      <c r="H96" s="30"/>
-      <c r="I96" s="30"/>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="30"/>
-      <c r="B97" s="30" t="s">
+      <c r="C96" s="25"/>
+      <c r="D96" s="25"/>
+      <c r="E96" s="25"/>
+      <c r="F96" s="25"/>
+      <c r="G96" s="25"/>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="25"/>
+      <c r="B97" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="C97" s="30"/>
-      <c r="D97" s="30"/>
-      <c r="E97" s="30"/>
-      <c r="F97" s="30"/>
-      <c r="G97" s="30"/>
-      <c r="H97" s="30"/>
-      <c r="I97" s="30"/>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" s="30"/>
-      <c r="B98" s="30" t="s">
+      <c r="C97" s="25"/>
+      <c r="D97" s="25"/>
+      <c r="E97" s="25"/>
+      <c r="F97" s="25"/>
+      <c r="G97" s="25"/>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="25"/>
+      <c r="B98" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="C98" s="30"/>
-      <c r="D98" s="30"/>
-      <c r="E98" s="30"/>
-      <c r="F98" s="30"/>
-      <c r="G98" s="30"/>
-      <c r="H98" s="30"/>
-      <c r="I98" s="30"/>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B99" s="30" t="s">
+      <c r="C98" s="25"/>
+      <c r="D98" s="25"/>
+      <c r="E98" s="25"/>
+      <c r="F98" s="25"/>
+      <c r="G98" s="25"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B99" s="25" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="H3:J3"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.2" right="0.2" top="0.19027777777777777" bottom="0.39374999999999999" header="0.51180555555555551" footer="0.51180555555555551"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
